--- a/Agentes/Maria/Sistemas de RH/Relatórios/2026-08/Análise de Batidas Faltantes - Maio a Julho 2026.xlsx
+++ b/Agentes/Maria/Sistemas de RH/Relatórios/2026-08/Análise de Batidas Faltantes - Maio a Julho 2026.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critérios e ressalvas" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo mensal'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo mensal'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Por unidade'!$A$1:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Por departamento'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Por horário'!$A$1:$D$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Reincidência'!$A$1:$D$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ocorrências nominais'!$A$1:$L$290</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Critérios e ressalvas'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Ocorrências nominais'!$A$1:$M$290</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Critérios e ressalvas'!$A$1:$B$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -453,11 +453,13 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,25 +490,35 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Ímpares confirmadas na fonte</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Divergências espelho x fonte</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Sem horário pendente</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Sem horário justificado</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Folgas</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Rótulos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Afastamentos sobrepostos</t>
         </is>
@@ -531,18 +543,24 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>99</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>634</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>529</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>134</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>111</v>
       </c>
     </row>
@@ -565,18 +583,24 @@
         <v>4</v>
       </c>
       <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>85</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>544</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>386</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>188</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>160</v>
       </c>
     </row>
@@ -599,23 +623,29 @@
         <v>19</v>
       </c>
       <c r="F4" t="n">
+        <v>18</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>80</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>586</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>412</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>213</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>190</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1338,7 +1368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L290"/>
+  <dimension ref="A1:M290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1348,11 +1378,12 @@
     <col width="29" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
-    <col width="43" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1408,10 +1439,15 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Eventos na fonte bruta</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Padrão de horários</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Observação</t>
         </is>
@@ -1466,8 +1502,11 @@
       <c r="J2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,8 +1557,11 @@
       <c r="J3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1570,8 +1612,11 @@
       <c r="J4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1622,8 +1667,11 @@
       <c r="J5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1674,8 +1722,11 @@
       <c r="J6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1726,8 +1777,11 @@
       <c r="J7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1778,8 +1832,11 @@
       <c r="J8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1830,8 +1887,11 @@
       <c r="J9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1882,8 +1942,11 @@
       <c r="J10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1934,8 +1997,11 @@
       <c r="J11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1986,8 +2052,11 @@
       <c r="J12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2038,8 +2107,11 @@
       <c r="J13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2090,8 +2162,11 @@
       <c r="J14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2142,8 +2217,11 @@
       <c r="J15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2194,8 +2272,11 @@
       <c r="J16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2246,8 +2327,11 @@
       <c r="J17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2298,8 +2382,11 @@
       <c r="J18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2350,8 +2437,11 @@
       <c r="J19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2402,8 +2492,11 @@
       <c r="J20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2454,8 +2547,11 @@
       <c r="J21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2506,8 +2602,11 @@
       <c r="J22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2558,8 +2657,11 @@
       <c r="J23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2610,8 +2712,11 @@
       <c r="J24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2662,8 +2767,11 @@
       <c r="J25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2714,8 +2822,11 @@
       <c r="J26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2766,8 +2877,11 @@
       <c r="J27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2818,8 +2932,11 @@
       <c r="J28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2870,8 +2987,11 @@
       <c r="J29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2922,8 +3042,11 @@
       <c r="J30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2974,8 +3097,11 @@
       <c r="J31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3026,8 +3152,11 @@
       <c r="J32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3078,8 +3207,11 @@
       <c r="J33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3130,8 +3262,11 @@
       <c r="J34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3182,8 +3317,11 @@
       <c r="J35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3234,8 +3372,11 @@
       <c r="J36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3286,8 +3427,11 @@
       <c r="J37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3338,8 +3482,11 @@
       <c r="J38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3390,8 +3537,11 @@
       <c r="J39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3442,8 +3592,11 @@
       <c r="J40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3494,8 +3647,11 @@
       <c r="J41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3546,8 +3702,11 @@
       <c r="J42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3598,8 +3757,11 @@
       <c r="J43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3650,8 +3812,11 @@
       <c r="J44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3702,8 +3867,11 @@
       <c r="J45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3754,8 +3922,11 @@
       <c r="J46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3806,8 +3977,11 @@
       <c r="J47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3858,8 +4032,11 @@
       <c r="J48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3910,8 +4087,11 @@
       <c r="J49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3962,8 +4142,11 @@
       <c r="J50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4014,8 +4197,11 @@
       <c r="J51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4066,8 +4252,11 @@
       <c r="J52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4118,8 +4307,11 @@
       <c r="J53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4170,8 +4362,11 @@
       <c r="J54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4222,8 +4417,11 @@
       <c r="J55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4274,8 +4472,11 @@
       <c r="J56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4326,8 +4527,11 @@
       <c r="J57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4378,8 +4582,11 @@
       <c r="J58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4419,7 +4626,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4430,12 +4637,15 @@
       <c r="J59" t="n">
         <v>5</v>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" t="n">
+        <v>5</v>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>Entrada1=08:12 | Saida1=12:24 | Entrada2=12:35 | Saida2=13:25 | Entrada3=14:46</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4486,8 +4696,11 @@
       <c r="J60" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4538,8 +4751,11 @@
       <c r="J61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4590,8 +4806,11 @@
       <c r="J62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4642,8 +4861,11 @@
       <c r="J63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4694,8 +4916,11 @@
       <c r="J64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4746,8 +4971,11 @@
       <c r="J65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4798,8 +5026,11 @@
       <c r="J66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4850,8 +5081,11 @@
       <c r="J67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4902,8 +5136,11 @@
       <c r="J68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4954,8 +5191,11 @@
       <c r="J69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -5006,8 +5246,11 @@
       <c r="J70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -5058,8 +5301,11 @@
       <c r="J71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -5110,8 +5356,11 @@
       <c r="J72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -5162,8 +5411,11 @@
       <c r="J73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -5214,8 +5466,11 @@
       <c r="J74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -5266,8 +5521,11 @@
       <c r="J75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -5318,8 +5576,11 @@
       <c r="J76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -5370,8 +5631,11 @@
       <c r="J77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5422,8 +5686,11 @@
       <c r="J78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5474,8 +5741,11 @@
       <c r="J79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -5526,8 +5796,11 @@
       <c r="J80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -5578,8 +5851,11 @@
       <c r="J81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5630,8 +5906,11 @@
       <c r="J82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5682,8 +5961,11 @@
       <c r="J83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5734,8 +6016,11 @@
       <c r="J84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5786,8 +6071,11 @@
       <c r="J85" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5838,8 +6126,11 @@
       <c r="J86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5890,8 +6181,11 @@
       <c r="J87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5942,8 +6236,11 @@
       <c r="J88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5994,8 +6291,11 @@
       <c r="J89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -6046,8 +6346,11 @@
       <c r="J90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -6098,8 +6401,11 @@
       <c r="J91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -6150,8 +6456,11 @@
       <c r="J92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -6202,8 +6511,11 @@
       <c r="J93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -6254,8 +6566,11 @@
       <c r="J94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -6306,8 +6621,11 @@
       <c r="J95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -6358,8 +6676,11 @@
       <c r="J96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -6410,8 +6731,11 @@
       <c r="J97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6462,8 +6786,11 @@
       <c r="J98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6514,8 +6841,11 @@
       <c r="J99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6555,7 +6885,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6566,12 +6896,15 @@
       <c r="J100" t="n">
         <v>3</v>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K100" t="n">
+        <v>3</v>
+      </c>
+      <c r="L100" t="inlineStr">
         <is>
           <t>Entrada1=10:36 | Saida1=13:46 | Entrada2=18:05</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6622,8 +6955,11 @@
       <c r="J101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6674,8 +7010,11 @@
       <c r="J102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6726,8 +7065,11 @@
       <c r="J103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6778,8 +7120,11 @@
       <c r="J104" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6830,8 +7175,11 @@
       <c r="J105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6882,8 +7230,11 @@
       <c r="J106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6934,8 +7285,11 @@
       <c r="J107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6986,8 +7340,11 @@
       <c r="J108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -7038,8 +7395,11 @@
       <c r="J109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -7090,8 +7450,11 @@
       <c r="J110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -7142,8 +7505,11 @@
       <c r="J111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -7194,8 +7560,11 @@
       <c r="J112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K112" s="2" t="inlineStr"/>
+      <c r="K112" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -7246,8 +7615,11 @@
       <c r="J113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K113" s="2" t="inlineStr"/>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -7298,8 +7670,11 @@
       <c r="J114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K114" s="2" t="inlineStr"/>
+      <c r="K114" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -7350,8 +7725,11 @@
       <c r="J115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K115" s="2" t="inlineStr"/>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -7402,8 +7780,11 @@
       <c r="J116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K116" s="2" t="inlineStr"/>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -7454,8 +7835,11 @@
       <c r="J117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K117" s="2" t="inlineStr"/>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -7506,8 +7890,11 @@
       <c r="J118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K118" s="2" t="inlineStr"/>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -7558,8 +7945,11 @@
       <c r="J119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K119" s="2" t="inlineStr"/>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -7610,8 +8000,11 @@
       <c r="J120" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K120" s="2" t="inlineStr"/>
+      <c r="K120" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -7662,8 +8055,11 @@
       <c r="J121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K121" s="2" t="inlineStr"/>
+      <c r="K121" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -7714,8 +8110,11 @@
       <c r="J122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K122" s="2" t="inlineStr"/>
+      <c r="K122" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -7766,8 +8165,11 @@
       <c r="J123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K123" s="2" t="inlineStr"/>
+      <c r="K123" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7818,8 +8220,11 @@
       <c r="J124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K124" s="2" t="inlineStr"/>
+      <c r="K124" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -7870,8 +8275,11 @@
       <c r="J125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K125" s="2" t="inlineStr"/>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -7922,8 +8330,11 @@
       <c r="J126" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K126" s="2" t="inlineStr"/>
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -7974,8 +8385,11 @@
       <c r="J127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -8026,8 +8440,11 @@
       <c r="J128" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -8078,8 +8495,11 @@
       <c r="J129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -8130,8 +8550,11 @@
       <c r="J130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -8182,8 +8605,11 @@
       <c r="J131" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -8234,8 +8660,11 @@
       <c r="J132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -8286,8 +8715,11 @@
       <c r="J133" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -8338,8 +8770,11 @@
       <c r="J134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -8390,8 +8825,11 @@
       <c r="J135" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -8442,8 +8880,11 @@
       <c r="J136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -8494,8 +8935,11 @@
       <c r="J137" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -8546,8 +8990,11 @@
       <c r="J138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -8598,8 +9045,11 @@
       <c r="J139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -8650,8 +9100,11 @@
       <c r="J140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -8702,8 +9155,11 @@
       <c r="J141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -8754,8 +9210,11 @@
       <c r="J142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8806,8 +9265,11 @@
       <c r="J143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -8858,8 +9320,11 @@
       <c r="J144" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -8910,8 +9375,11 @@
       <c r="J145" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -8962,8 +9430,11 @@
       <c r="J146" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -9014,8 +9485,11 @@
       <c r="J147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -9066,8 +9540,11 @@
       <c r="J148" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -9118,8 +9595,11 @@
       <c r="J149" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -9170,8 +9650,11 @@
       <c r="J150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -9222,8 +9705,11 @@
       <c r="J151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -9274,8 +9760,11 @@
       <c r="J152" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -9326,8 +9815,11 @@
       <c r="J153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -9378,8 +9870,11 @@
       <c r="J154" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -9430,8 +9925,11 @@
       <c r="J155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -9482,8 +9980,11 @@
       <c r="J156" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -9534,8 +10035,11 @@
       <c r="J157" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -9586,8 +10090,11 @@
       <c r="J158" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -9638,8 +10145,11 @@
       <c r="J159" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -9690,8 +10200,11 @@
       <c r="J160" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -9742,8 +10255,11 @@
       <c r="J161" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -9794,8 +10310,11 @@
       <c r="J162" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -9846,8 +10365,11 @@
       <c r="J163" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -9898,8 +10420,11 @@
       <c r="J164" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -9950,8 +10475,11 @@
       <c r="J165" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -10002,8 +10530,11 @@
       <c r="J166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -10054,8 +10585,11 @@
       <c r="J167" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -10106,8 +10640,11 @@
       <c r="J168" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -10158,8 +10695,11 @@
       <c r="J169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -10210,8 +10750,11 @@
       <c r="J170" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -10262,8 +10805,11 @@
       <c r="J171" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -10314,8 +10860,11 @@
       <c r="J172" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -10366,8 +10915,11 @@
       <c r="J173" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K173" s="2" t="inlineStr"/>
+      <c r="K173" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10407,7 +10959,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -10418,12 +10970,15 @@
       <c r="J174" t="n">
         <v>5</v>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="K174" t="n">
+        <v>5</v>
+      </c>
+      <c r="L174" t="inlineStr">
         <is>
           <t>Entrada1=08:00 | Saida1=12:46 | Entrada2=13:46 | Saida2=17:48 | Entrada3=17:47</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -10474,8 +11029,11 @@
       <c r="J175" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K175" s="2" t="inlineStr"/>
+      <c r="K175" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -10526,8 +11084,11 @@
       <c r="J176" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K176" s="2" t="inlineStr"/>
+      <c r="K176" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -10578,8 +11139,11 @@
       <c r="J177" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K177" s="2" t="inlineStr"/>
+      <c r="K177" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -10630,8 +11194,11 @@
       <c r="J178" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10671,7 +11238,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10682,12 +11249,15 @@
       <c r="J179" t="n">
         <v>5</v>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="K179" t="n">
+        <v>5</v>
+      </c>
+      <c r="L179" t="inlineStr">
         <is>
           <t>Entrada1=08:00 | Saida1=13:09 | Entrada2=14:09 | Saida2=14:09 | Entrada3=17:47</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -10738,8 +11308,11 @@
       <c r="J180" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10779,7 +11352,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -10790,12 +11363,15 @@
       <c r="J181" t="n">
         <v>5</v>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="K181" t="n">
+        <v>5</v>
+      </c>
+      <c r="L181" t="inlineStr">
         <is>
           <t>Entrada1=07:56 | Saida1=13:06 | Entrada2=14:06 | Saida2=14:06 | Entrada3=17:54</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10846,8 +11422,11 @@
       <c r="J182" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -10898,8 +11477,11 @@
       <c r="J183" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L183" s="2" t="inlineStr"/>
+      <c r="M183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10950,8 +11532,11 @@
       <c r="J184" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L184" s="2" t="inlineStr"/>
+      <c r="M184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10991,7 +11576,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11002,12 +11587,15 @@
       <c r="J185" t="n">
         <v>5</v>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="K185" t="n">
+        <v>5</v>
+      </c>
+      <c r="L185" t="inlineStr">
         <is>
           <t>Entrada1=09:00 | Saida1=09:00 | Entrada2=11:44 | Saida2=12:43 | Entrada3=16:57</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -11058,8 +11646,11 @@
       <c r="J186" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -11110,8 +11701,11 @@
       <c r="J187" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L187" s="2" t="inlineStr"/>
+      <c r="M187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -11162,8 +11756,11 @@
       <c r="J188" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K188" s="2" t="inlineStr"/>
+      <c r="K188" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -11214,8 +11811,11 @@
       <c r="J189" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K189" s="2" t="inlineStr"/>
+      <c r="K189" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L189" s="2" t="inlineStr"/>
+      <c r="M189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -11266,8 +11866,11 @@
       <c r="J190" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K190" s="2" t="inlineStr"/>
+      <c r="K190" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -11318,8 +11921,11 @@
       <c r="J191" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K191" s="2" t="inlineStr"/>
+      <c r="K191" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L191" s="2" t="inlineStr"/>
+      <c r="M191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -11370,8 +11976,11 @@
       <c r="J192" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K192" s="2" t="inlineStr"/>
+      <c r="K192" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -11422,8 +12031,11 @@
       <c r="J193" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K193" s="2" t="inlineStr"/>
+      <c r="K193" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -11474,8 +12086,11 @@
       <c r="J194" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K194" s="2" t="inlineStr"/>
+      <c r="K194" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L194" s="2" t="inlineStr"/>
+      <c r="M194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -11526,8 +12141,11 @@
       <c r="J195" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K195" s="2" t="inlineStr"/>
+      <c r="K195" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L195" s="2" t="inlineStr"/>
+      <c r="M195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -11578,8 +12196,11 @@
       <c r="J196" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K196" s="2" t="inlineStr"/>
+      <c r="K196" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L196" s="2" t="inlineStr"/>
+      <c r="M196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -11630,8 +12251,11 @@
       <c r="J197" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K197" s="2" t="inlineStr"/>
+      <c r="K197" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L197" s="2" t="inlineStr"/>
+      <c r="M197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -11682,8 +12306,11 @@
       <c r="J198" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K198" s="2" t="inlineStr"/>
+      <c r="K198" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L198" s="2" t="inlineStr"/>
+      <c r="M198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -11734,8 +12361,11 @@
       <c r="J199" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K199" s="2" t="inlineStr"/>
+      <c r="K199" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -11786,8 +12416,11 @@
       <c r="J200" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K200" s="2" t="inlineStr"/>
+      <c r="K200" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L200" s="2" t="inlineStr"/>
+      <c r="M200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -11838,8 +12471,11 @@
       <c r="J201" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K201" s="2" t="inlineStr"/>
+      <c r="K201" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L201" s="2" t="inlineStr"/>
+      <c r="M201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -11890,8 +12526,11 @@
       <c r="J202" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K202" s="2" t="inlineStr"/>
+      <c r="K202" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L202" s="2" t="inlineStr"/>
+      <c r="M202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -11942,8 +12581,11 @@
       <c r="J203" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K203" s="2" t="inlineStr"/>
+      <c r="K203" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L203" s="2" t="inlineStr"/>
+      <c r="M203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -11994,8 +12636,11 @@
       <c r="J204" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L204" s="2" t="inlineStr"/>
+      <c r="M204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -12046,8 +12691,11 @@
       <c r="J205" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L205" s="2" t="inlineStr"/>
+      <c r="M205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -12098,8 +12746,11 @@
       <c r="J206" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L206" s="2" t="inlineStr"/>
+      <c r="M206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -12150,8 +12801,11 @@
       <c r="J207" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L207" s="2" t="inlineStr"/>
+      <c r="M207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -12202,8 +12856,11 @@
       <c r="J208" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L208" s="2" t="inlineStr"/>
+      <c r="M208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -12254,8 +12911,11 @@
       <c r="J209" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -12306,8 +12966,11 @@
       <c r="J210" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -12358,8 +13021,11 @@
       <c r="J211" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -12410,8 +13076,11 @@
       <c r="J212" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L212" s="2" t="inlineStr"/>
+      <c r="M212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -12462,8 +13131,11 @@
       <c r="J213" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L213" s="2" t="inlineStr"/>
+      <c r="M213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -12514,8 +13186,11 @@
       <c r="J214" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L214" s="2" t="inlineStr"/>
+      <c r="M214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -12566,8 +13241,11 @@
       <c r="J215" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L215" s="2" t="inlineStr"/>
+      <c r="M215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -12618,8 +13296,11 @@
       <c r="J216" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L216" s="2" t="inlineStr"/>
+      <c r="M216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -12670,8 +13351,11 @@
       <c r="J217" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L217" s="2" t="inlineStr"/>
+      <c r="M217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -12722,8 +13406,11 @@
       <c r="J218" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L218" s="2" t="inlineStr"/>
+      <c r="M218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -12774,8 +13461,11 @@
       <c r="J219" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L219" s="2" t="inlineStr"/>
+      <c r="M219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -12826,8 +13516,11 @@
       <c r="J220" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L220" s="2" t="inlineStr"/>
+      <c r="M220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -12878,8 +13571,11 @@
       <c r="J221" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L221" s="2" t="inlineStr"/>
+      <c r="M221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -12930,8 +13626,11 @@
       <c r="J222" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L222" s="2" t="inlineStr"/>
+      <c r="M222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -12982,8 +13681,11 @@
       <c r="J223" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L223" s="2" t="inlineStr"/>
+      <c r="M223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -13034,8 +13736,11 @@
       <c r="J224" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L224" s="2" t="inlineStr"/>
+      <c r="M224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -13086,8 +13791,11 @@
       <c r="J225" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L225" s="2" t="inlineStr"/>
+      <c r="M225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -13138,8 +13846,11 @@
       <c r="J226" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L226" s="2" t="inlineStr"/>
+      <c r="M226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -13190,8 +13901,11 @@
       <c r="J227" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L227" s="2" t="inlineStr"/>
+      <c r="M227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -13242,8 +13956,11 @@
       <c r="J228" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L228" s="2" t="inlineStr"/>
+      <c r="M228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -13294,8 +14011,11 @@
       <c r="J229" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L229" s="2" t="inlineStr"/>
+      <c r="M229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -13346,8 +14066,11 @@
       <c r="J230" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L230" s="2" t="inlineStr"/>
+      <c r="M230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -13398,8 +14121,11 @@
       <c r="J231" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L231" s="2" t="inlineStr"/>
+      <c r="M231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -13450,8 +14176,11 @@
       <c r="J232" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L232" s="2" t="inlineStr"/>
+      <c r="M232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -13502,8 +14231,11 @@
       <c r="J233" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L233" s="2" t="inlineStr"/>
+      <c r="M233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -13554,8 +14286,11 @@
       <c r="J234" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L234" s="2" t="inlineStr"/>
+      <c r="M234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -13606,8 +14341,11 @@
       <c r="J235" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L235" s="2" t="inlineStr"/>
+      <c r="M235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -13658,8 +14396,11 @@
       <c r="J236" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L236" s="2" t="inlineStr"/>
+      <c r="M236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -13710,8 +14451,11 @@
       <c r="J237" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L237" s="2" t="inlineStr"/>
+      <c r="M237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -13762,8 +14506,11 @@
       <c r="J238" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L238" s="2" t="inlineStr"/>
+      <c r="M238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -13814,8 +14561,11 @@
       <c r="J239" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K239" s="2" t="inlineStr"/>
+      <c r="K239" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L239" s="2" t="inlineStr"/>
+      <c r="M239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -13866,8 +14616,11 @@
       <c r="J240" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K240" s="2" t="inlineStr"/>
+      <c r="K240" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L240" s="2" t="inlineStr"/>
+      <c r="M240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -13918,8 +14671,11 @@
       <c r="J241" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K241" s="2" t="inlineStr"/>
+      <c r="K241" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L241" s="2" t="inlineStr"/>
+      <c r="M241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -13970,8 +14726,11 @@
       <c r="J242" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L242" s="2" t="inlineStr"/>
+      <c r="M242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -14022,8 +14781,11 @@
       <c r="J243" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K243" s="2" t="inlineStr"/>
+      <c r="K243" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L243" s="2" t="inlineStr"/>
+      <c r="M243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -14074,8 +14836,11 @@
       <c r="J244" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L244" s="2" t="inlineStr"/>
+      <c r="M244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -14126,8 +14891,11 @@
       <c r="J245" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K245" s="2" t="inlineStr"/>
+      <c r="K245" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L245" s="2" t="inlineStr"/>
+      <c r="M245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -14178,8 +14946,11 @@
       <c r="J246" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K246" s="2" t="inlineStr"/>
+      <c r="K246" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L246" s="2" t="inlineStr"/>
+      <c r="M246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -14230,8 +15001,11 @@
       <c r="J247" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L247" s="2" t="inlineStr"/>
+      <c r="M247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -14282,8 +15056,11 @@
       <c r="J248" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L248" s="2" t="inlineStr"/>
+      <c r="M248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -14334,8 +15111,11 @@
       <c r="J249" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L249" s="2" t="inlineStr"/>
+      <c r="M249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -14386,8 +15166,11 @@
       <c r="J250" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L250" s="2" t="inlineStr"/>
+      <c r="M250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -14438,8 +15221,11 @@
       <c r="J251" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L251" s="2" t="inlineStr"/>
+      <c r="M251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -14490,8 +15276,11 @@
       <c r="J252" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L252" s="2" t="inlineStr"/>
+      <c r="M252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -14542,8 +15331,11 @@
       <c r="J253" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L253" s="2" t="inlineStr"/>
+      <c r="M253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -14594,8 +15386,11 @@
       <c r="J254" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L254" s="2" t="inlineStr"/>
+      <c r="M254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -14646,8 +15441,11 @@
       <c r="J255" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L255" s="2" t="inlineStr"/>
+      <c r="M255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -14698,8 +15496,11 @@
       <c r="J256" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L256" s="2" t="inlineStr"/>
+      <c r="M256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -14750,8 +15551,11 @@
       <c r="J257" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K257" s="2" t="inlineStr"/>
+      <c r="K257" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L257" s="2" t="inlineStr"/>
+      <c r="M257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -14802,8 +15606,11 @@
       <c r="J258" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L258" s="2" t="inlineStr"/>
+      <c r="M258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -14854,8 +15661,11 @@
       <c r="J259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L259" s="2" t="inlineStr"/>
+      <c r="M259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -14906,8 +15716,11 @@
       <c r="J260" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L260" s="2" t="inlineStr"/>
+      <c r="M260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -14958,8 +15771,11 @@
       <c r="J261" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K261" s="2" t="inlineStr"/>
+      <c r="K261" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L261" s="2" t="inlineStr"/>
+      <c r="M261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -15010,8 +15826,11 @@
       <c r="J262" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L262" s="2" t="inlineStr"/>
+      <c r="M262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15051,7 +15870,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -15062,12 +15881,15 @@
       <c r="J263" t="n">
         <v>5</v>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="K263" t="n">
+        <v>5</v>
+      </c>
+      <c r="L263" t="inlineStr">
         <is>
           <t>Entrada1=08:16 | Saida1=12:51 | Entrada2=13:51 | Saida2=17:40 | Entrada3=16:59</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -15118,8 +15940,11 @@
       <c r="J264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L264" s="2" t="inlineStr"/>
+      <c r="M264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -15170,8 +15995,11 @@
       <c r="J265" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K265" s="2" t="inlineStr"/>
+      <c r="K265" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L265" s="2" t="inlineStr"/>
+      <c r="M265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15211,7 +16039,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -15222,12 +16050,15 @@
       <c r="J266" t="n">
         <v>3</v>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="K266" t="n">
+        <v>3</v>
+      </c>
+      <c r="L266" t="inlineStr">
         <is>
           <t>Entrada1=08:59 | Saida1=13:42 | Entrada2=18:01</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -15278,8 +16109,11 @@
       <c r="J267" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L267" s="2" t="inlineStr"/>
+      <c r="M267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -15330,8 +16164,11 @@
       <c r="J268" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L268" s="2" t="inlineStr"/>
+      <c r="M268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15371,7 +16208,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -15382,12 +16219,15 @@
       <c r="J269" t="n">
         <v>3</v>
       </c>
-      <c r="K269" t="inlineStr">
+      <c r="K269" t="n">
+        <v>3</v>
+      </c>
+      <c r="L269" t="inlineStr">
         <is>
           <t>Entrada1=12:00 | Saida1=13:01 | Entrada2=17:48</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15427,7 +16267,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -15438,12 +16278,15 @@
       <c r="J270" t="n">
         <v>1</v>
       </c>
-      <c r="K270" t="inlineStr">
+      <c r="K270" t="n">
+        <v>1</v>
+      </c>
+      <c r="L270" t="inlineStr">
         <is>
           <t>Entrada1=17:00</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -15494,8 +16337,11 @@
       <c r="J271" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L271" s="2" t="inlineStr"/>
+      <c r="M271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -15546,64 +16392,70 @@
       <c r="J272" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L272" s="2" t="inlineStr"/>
+      <c r="M272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" t="inlineStr">
+      <c r="A273" s="2" t="inlineStr">
         <is>
           <t>Julho/2026</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr">
+      <c r="B273" s="2" t="inlineStr">
         <is>
           <t>28/07/2026</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
+      <c r="C273" s="2" t="inlineStr">
         <is>
           <t>CONAMORE SSL CAMA MESA E BANHO LTDA FILIAL</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>SUPRIMENTOS</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>AUX ALMOXARIFADO/ CORTE</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>CONFECÇÃO</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr">
         <is>
           <t>RONALDO PESTANA</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>Marcação ímpar — provável batida faltante</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>Divergência espelho x fonte — exige conciliação</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
         <is>
           <t>Retorno do intervalo</t>
         </is>
       </c>
-      <c r="J273" t="n">
+      <c r="J273" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="K273" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L273" s="2" t="inlineStr">
         <is>
           <t>Entrada1=07:59 | Saida1=12:46 | Saida2=17:47</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr"/>
+      <c r="M273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15643,7 +16495,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -15654,12 +16506,15 @@
       <c r="J274" t="n">
         <v>3</v>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="K274" t="n">
+        <v>3</v>
+      </c>
+      <c r="L274" t="inlineStr">
         <is>
           <t>Entrada1=07:58 | Saida1=12:21 | Entrada2=18:09</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15699,7 +16554,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -15710,12 +16565,15 @@
       <c r="J275" t="n">
         <v>3</v>
       </c>
-      <c r="K275" t="inlineStr">
+      <c r="K275" t="n">
+        <v>3</v>
+      </c>
+      <c r="L275" t="inlineStr">
         <is>
           <t>Entrada1=08:56 | Saida1=13:57 | Entrada2=17:59</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15755,7 +16613,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -15766,12 +16624,15 @@
       <c r="J276" t="n">
         <v>1</v>
       </c>
-      <c r="K276" t="inlineStr">
+      <c r="K276" t="n">
+        <v>1</v>
+      </c>
+      <c r="L276" t="inlineStr">
         <is>
           <t>Entrada1=17:45</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15811,7 +16672,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -15822,12 +16683,15 @@
       <c r="J277" t="n">
         <v>3</v>
       </c>
-      <c r="K277" t="inlineStr">
+      <c r="K277" t="n">
+        <v>3</v>
+      </c>
+      <c r="L277" t="inlineStr">
         <is>
           <t>Entrada1=07:44 | Saida1=12:21 | Entrada2=18:09</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15867,7 +16731,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -15878,12 +16742,15 @@
       <c r="J278" t="n">
         <v>5</v>
       </c>
-      <c r="K278" t="inlineStr">
+      <c r="K278" t="n">
+        <v>5</v>
+      </c>
+      <c r="L278" t="inlineStr">
         <is>
           <t>Entrada1=07:56 | Saida1=12:18 | Entrada2=13:21 | Saida2=14:07 | Entrada3=17:48</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -15923,7 +16790,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -15934,12 +16801,15 @@
       <c r="J279" t="n">
         <v>3</v>
       </c>
-      <c r="K279" t="inlineStr">
+      <c r="K279" t="n">
+        <v>3</v>
+      </c>
+      <c r="L279" t="inlineStr">
         <is>
           <t>Entrada1=07:52 | Saida1=12:21 | Entrada2=18:03</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15979,7 +16849,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -15990,12 +16860,15 @@
       <c r="J280" t="n">
         <v>3</v>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="K280" t="n">
+        <v>3</v>
+      </c>
+      <c r="L280" t="inlineStr">
         <is>
           <t>Entrada1=08:11 | Saida1=12:21 | Entrada2=17:55</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -16035,7 +16908,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -16046,12 +16919,15 @@
       <c r="J281" t="n">
         <v>3</v>
       </c>
-      <c r="K281" t="inlineStr">
+      <c r="K281" t="n">
+        <v>3</v>
+      </c>
+      <c r="L281" t="inlineStr">
         <is>
           <t>Entrada1=08:08 | Saida1=12:21 | Entrada2=17:50</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16091,7 +16967,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -16102,12 +16978,15 @@
       <c r="J282" t="n">
         <v>3</v>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="K282" t="n">
+        <v>3</v>
+      </c>
+      <c r="L282" t="inlineStr">
         <is>
           <t>Entrada1=07:58 | Saida1=12:20 | Entrada2=17:55</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16147,7 +17026,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -16158,12 +17037,15 @@
       <c r="J283" t="n">
         <v>3</v>
       </c>
-      <c r="K283" t="inlineStr">
+      <c r="K283" t="n">
+        <v>3</v>
+      </c>
+      <c r="L283" t="inlineStr">
         <is>
           <t>Entrada1=12:21 | Saida1=13:20 | Entrada2=17:49</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16203,7 +17085,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -16214,12 +17096,15 @@
       <c r="J284" t="n">
         <v>3</v>
       </c>
-      <c r="K284" t="inlineStr">
+      <c r="K284" t="n">
+        <v>3</v>
+      </c>
+      <c r="L284" t="inlineStr">
         <is>
           <t>Entrada1=08:02 | Saida1=12:21 | Entrada2=17:53</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16259,7 +17144,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -16270,12 +17155,15 @@
       <c r="J285" t="n">
         <v>3</v>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="K285" t="n">
+        <v>3</v>
+      </c>
+      <c r="L285" t="inlineStr">
         <is>
           <t>Entrada1=12:45 | Saida1=13:45 | Entrada2=17:47</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -16326,8 +17214,11 @@
       <c r="J286" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L286" s="2" t="inlineStr"/>
+      <c r="M286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16367,7 +17258,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -16378,12 +17269,15 @@
       <c r="J287" t="n">
         <v>1</v>
       </c>
-      <c r="K287" t="inlineStr">
+      <c r="K287" t="n">
+        <v>1</v>
+      </c>
+      <c r="L287" t="inlineStr">
         <is>
           <t>Entrada1=17:45</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16423,7 +17317,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Marcação ímpar — provável batida faltante</t>
+          <t>Marcação ímpar confirmada na fonte — provável batida faltante</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -16434,12 +17328,15 @@
       <c r="J288" t="n">
         <v>3</v>
       </c>
-      <c r="K288" t="inlineStr">
+      <c r="K288" t="n">
+        <v>3</v>
+      </c>
+      <c r="L288" t="inlineStr">
         <is>
           <t>Entrada1=07:56 | Saida1=13:03 | Entrada2=14:06</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -16490,8 +17387,11 @@
       <c r="J289" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K289" s="2" t="inlineStr"/>
+      <c r="K289" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L289" s="2" t="inlineStr"/>
+      <c r="M289" s="2" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -16542,11 +17442,14 @@
       <c r="J290" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="K290" s="2" t="inlineStr"/>
+      <c r="K290" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="L290" s="2" t="inlineStr"/>
+      <c r="M290" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L290"/>
+  <autoFilter ref="A1:M290"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16557,10 +17460,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -16591,53 +17494,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sem horário pendente</t>
+          <t>Validação na fonte</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dia fora de folga, sem rótulo e sem afastamento localizado. Pode ser falta, escala, abono ou ajuste; não é ausência confirmada.</t>
+          <t>A marcação ímpar é reforçada quando a FonteDados também contém quantidade ímpar de eventos no mesmo colaborador/dia.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sem horário justificado</t>
+          <t>Divergência espelho x fonte</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Linha sem horários coberta por folga, rótulo do espelho ou afastamento localizado.</t>
+          <t>O espelho tem quantidade ímpar, mas a FonteDados tem quantidade par; conciliar processamento/ajuste antes de classificar.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Histórico</t>
+          <t>Sem horário pendente</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Filtro considera admissão e demissão na data. Dados cadastrais atuais podem não refletir transferências históricas de unidade, setor ou horário.</t>
+          <t>Dia fora de folga, sem rótulo e sem afastamento localizado. Pode ser falta, escala, abono ou ajuste; não é ausência confirmada.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Sem horário justificado</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Linha sem horários coberta por folga, rótulo do espelho ou afastamento localizado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Histórico</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Filtro considera admissão e demissão na data. Dados cadastrais atuais podem não refletir transferências históricas de unidade, setor ou horário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Uso</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Documento confidencial, restrito a RH e direção. Não usar isoladamente para desconto ou medida disciplinar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>